--- a/TestStudentUpload.xlsx
+++ b/TestStudentUpload.xlsx
@@ -684,7 +684,7 @@
     <t>Local Guardian Address</t>
   </si>
   <si>
-    <t>Test Student new1</t>
+    <t>Test Student new16</t>
   </si>
   <si>
     <t>Male</t>
